--- a/data/trans_orig/IQ17A-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ17A-Estudios-trans_orig.xlsx
@@ -1180,7 +1180,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3234</t>
+          <t>3548</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3208</t>
+          <t>3242</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,99%</t>
         </is>
       </c>
     </row>
@@ -1397,12 +1397,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>614</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5070</t>
+          <t>5407</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1412,12 +1412,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4219</t>
+          <t>4164</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>1334</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6774</t>
+          <t>6912</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>17,02%</t>
         </is>
       </c>
     </row>
@@ -1508,12 +1508,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14100</t>
+          <t>13998</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19256</t>
+          <t>19330</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1523,12 +1523,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>70,58%</t>
+          <t>70,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>16402</t>
+          <t>16457</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,54%</t>
+          <t>79,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>32928</t>
+          <t>32729</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>39187</t>
+          <t>38723</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1593,12 +1593,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,1%</t>
+          <t>80,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>95,38%</t>
         </is>
       </c>
     </row>
@@ -1963,7 +1963,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2247</t>
+          <t>1869</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1998,7 +1998,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3220</t>
+          <t>3913</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2033,7 +2033,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>4420</t>
+          <t>4193</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4897</t>
+          <t>3392</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3320</t>
+          <t>3393</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1657</t>
+          <t>1509</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9527</t>
+          <t>8525</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1512</t>
+          <t>1425</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>8841</t>
+          <t>8191</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -2402,12 +2402,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4930</t>
+          <t>4732</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14119</t>
+          <t>13366</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2417,12 +2417,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2437,12 +2437,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4660</t>
+          <t>4252</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14199</t>
+          <t>13427</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10745</t>
+          <t>11029</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>23027</t>
+          <t>23649</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,8%</t>
         </is>
       </c>
     </row>
@@ -2513,12 +2513,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>64345</t>
+          <t>64825</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>73443</t>
+          <t>73751</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2528,12 +2528,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>82,33%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2548,12 +2548,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>85594</t>
+          <t>86185</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>96896</t>
+          <t>97678</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>81,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>155331</t>
+          <t>154176</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>168888</t>
+          <t>168419</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>83,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,18%</t>
         </is>
       </c>
     </row>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3228</t>
+          <t>3172</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3260,7 +3260,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2962</t>
+          <t>3213</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3275,7 +3275,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,84%</t>
         </is>
       </c>
     </row>
@@ -3412,7 +3412,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2727</t>
+          <t>2719</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3427,7 +3427,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3482,7 +3482,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2655</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>29080</t>
+          <t>29088</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3553,7 +3553,7 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>31376</t>
+          <t>31432</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,83%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3588,7 +3588,7 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>62259</t>
+          <t>62272</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
@@ -3603,7 +3603,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2036</t>
+          <t>2150</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -3988,7 +3988,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4008,7 +4008,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>3479</t>
+          <t>3497</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4023,7 +4023,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4043,7 +4043,7 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>3852</t>
+          <t>3906</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4058,7 +4058,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -4195,7 +4195,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>3663</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4210,7 +4210,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>4529</t>
+          <t>4647</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4265,7 +4265,7 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>5762</t>
+          <t>5306</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4280,7 +4280,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -4336,12 +4336,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1886</t>
+          <t>1507</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>8892</t>
+          <t>8989</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4351,12 +4351,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1378</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>8622</t>
+          <t>8736</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4386,12 +4386,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -4412,12 +4412,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>6736</t>
+          <t>6574</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>17256</t>
+          <t>16176</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4427,12 +4427,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>5431</t>
+          <t>5622</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>15349</t>
+          <t>15584</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4462,47 +4462,47 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
+          <t>9,67%</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>20384</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>13854</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>27760</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>6,99%</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>4,75%</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
           <t>9,52%</t>
-        </is>
-      </c>
-      <c r="Q37" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="R37" s="2" t="inlineStr">
-        <is>
-          <t>20384</t>
-        </is>
-      </c>
-      <c r="S37" s="2" t="inlineStr">
-        <is>
-          <t>14235</t>
-        </is>
-      </c>
-      <c r="T37" s="2" t="inlineStr">
-        <is>
-          <t>28200</t>
-        </is>
-      </c>
-      <c r="U37" s="2" t="inlineStr">
-        <is>
-          <t>6,99%</t>
-        </is>
-      </c>
-      <c r="V37" s="2" t="inlineStr">
-        <is>
-          <t>4,88%</t>
-        </is>
-      </c>
-      <c r="W37" s="2" t="inlineStr">
-        <is>
-          <t>9,67%</t>
         </is>
       </c>
     </row>
@@ -4523,12 +4523,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>112530</t>
+          <t>113352</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>122943</t>
+          <t>123541</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4538,12 +4538,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>86,85%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>137939</t>
+          <t>137779</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>150775</t>
+          <t>150836</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4573,12 +4573,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>85,47%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4593,12 +4593,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>255165</t>
+          <t>256012</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>271096</t>
+          <t>271506</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>87,47%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>93,07%</t>
         </is>
       </c>
     </row>
@@ -5542,7 +5542,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4453</t>
+          <t>3857</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5557,7 +5557,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2729</t>
+          <t>3294</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>5047</t>
+          <t>4621</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>12,85%</t>
         </is>
       </c>
     </row>
@@ -5648,12 +5648,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>660</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5453</t>
+          <t>5468</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5663,12 +5663,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5683,12 +5683,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2553</t>
+          <t>2499</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8436</t>
+          <t>8899</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5698,12 +5698,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,62%</t>
+          <t>51,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5718,12 +5718,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3836</t>
+          <t>3771</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11998</t>
+          <t>11406</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5733,12 +5733,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>31,71%</t>
         </is>
       </c>
     </row>
@@ -5759,12 +5759,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11752</t>
+          <t>12005</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17329</t>
+          <t>17430</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5774,12 +5774,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>63,13%</t>
+          <t>64,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5794,12 +5794,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8367</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14211</t>
+          <t>14685</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5809,12 +5809,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>48,22%</t>
+          <t>46,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>84,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5829,12 +5829,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>21792</t>
+          <t>22171</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>30522</t>
+          <t>30888</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5844,12 +5844,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>60,59%</t>
+          <t>61,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>85,88%</t>
         </is>
       </c>
     </row>
@@ -6214,7 +6214,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2893</t>
+          <t>2597</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6229,7 +6229,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -6284,7 +6284,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2754</t>
+          <t>2685</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6299,7 +6299,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -6471,7 +6471,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4630</t>
+          <t>4660</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6486,7 +6486,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6506,7 +6506,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>4510</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6521,7 +6521,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -6547,7 +6547,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>5473</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6562,7 +6562,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>882</t>
+          <t>890</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7476</t>
+          <t>7997</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6592,12 +6592,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6612,12 +6612,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1868</t>
+          <t>1579</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>10271</t>
+          <t>9693</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6627,12 +6627,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,41%</t>
         </is>
       </c>
     </row>
@@ -6653,12 +6653,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4161</t>
+          <t>4217</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13362</t>
+          <t>13574</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6668,12 +6668,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6688,12 +6688,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9052</t>
+          <t>9422</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21017</t>
+          <t>20636</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6703,12 +6703,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6723,12 +6723,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>15554</t>
+          <t>15019</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>30588</t>
+          <t>30539</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6738,12 +6738,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,88%</t>
         </is>
       </c>
     </row>
@@ -6764,12 +6764,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>82566</t>
+          <t>83327</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>93653</t>
+          <t>93497</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6779,12 +6779,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>83,95%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>94655</t>
+          <t>94398</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>108167</t>
+          <t>107396</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>78,18%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>88,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>181673</t>
+          <t>181689</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>198390</t>
+          <t>199206</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6854,7 +6854,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>90,55%</t>
         </is>
       </c>
     </row>
@@ -7547,12 +7547,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1251</t>
+          <t>1238</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>6756</t>
+          <t>7876</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -7587,7 +7587,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3597</t>
+          <t>3785</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -7602,7 +7602,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -7617,12 +7617,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1411</t>
+          <t>1451</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7639</t>
+          <t>8177</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -7632,12 +7632,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>11,03%</t>
         </is>
       </c>
     </row>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2178</t>
+          <t>2194</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>9589</t>
+          <t>10117</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7693,12 +7693,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2164</t>
+          <t>2110</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>9411</t>
+          <t>9168</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7708,12 +7708,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7728,12 +7728,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>6056</t>
+          <t>6003</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>16236</t>
+          <t>15737</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7743,12 +7743,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>21,23%</t>
         </is>
       </c>
     </row>
@@ -7769,12 +7769,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>29831</t>
+          <t>29408</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>38331</t>
+          <t>38454</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7784,12 +7784,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>69,38%</t>
+          <t>68,4%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7804,12 +7804,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>20902</t>
+          <t>21296</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>28297</t>
+          <t>28490</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7819,12 +7819,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>67,13%</t>
+          <t>68,4%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7839,12 +7839,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>53685</t>
+          <t>53429</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>64996</t>
+          <t>64883</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>72,42%</t>
+          <t>72,07%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>87,52%</t>
         </is>
       </c>
     </row>
@@ -8224,7 +8224,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2254</t>
+          <t>2441</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8294,7 +8294,7 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>2386</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8309,7 +8309,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
     </row>
@@ -8481,7 +8481,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>4537</t>
+          <t>4086</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -8496,7 +8496,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -8516,7 +8516,7 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>5258</t>
+          <t>4085</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -8531,7 +8531,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -8552,12 +8552,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2826</t>
+          <t>2809</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>10876</t>
+          <t>10690</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8567,12 +8567,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8587,12 +8587,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1638</t>
+          <t>1938</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>9281</t>
+          <t>9366</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8602,12 +8602,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8622,12 +8622,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>6356</t>
+          <t>6452</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>16465</t>
+          <t>17778</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8637,12 +8637,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,39%</t>
         </is>
       </c>
     </row>
@@ -8663,12 +8663,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>9690</t>
+          <t>10055</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>22806</t>
+          <t>22396</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8678,12 +8678,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8698,12 +8698,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>17894</t>
+          <t>17528</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>32879</t>
+          <t>32392</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>31580</t>
+          <t>30945</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>50277</t>
+          <t>51633</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8748,12 +8748,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,64%</t>
         </is>
       </c>
     </row>
@@ -8774,12 +8774,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>131835</t>
+          <t>131183</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>145991</t>
+          <t>145161</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8789,12 +8789,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>81,95%</t>
+          <t>81,54%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8809,12 +8809,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>129908</t>
+          <t>129320</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>146002</t>
+          <t>146589</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>76,76%</t>
+          <t>76,42%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>86,62%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>265711</t>
+          <t>265382</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>287091</t>
+          <t>287705</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>80,49%</t>
+          <t>80,39%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>87,16%</t>
         </is>
       </c>
     </row>
@@ -9349,7 +9349,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3481</t>
+          <t>2782</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9364,7 +9364,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9419,7 +9419,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>3261</t>
+          <t>2774</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9434,7 +9434,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>8,85%</t>
         </is>
       </c>
     </row>
@@ -9682,7 +9682,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2633</t>
+          <t>3286</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9697,7 +9697,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9752,7 +9752,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2584</t>
+          <t>3436</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9767,7 +9767,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>10,96%</t>
         </is>
       </c>
     </row>
@@ -9899,12 +9899,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>643</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6242</t>
+          <t>5515</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9914,12 +9914,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>28,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9939,7 +9939,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3995</t>
+          <t>3746</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9954,7 +9954,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7455</t>
+          <t>7565</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9989,7 +9989,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>24,14%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12420</t>
+          <t>12321</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17971</t>
+          <t>17947</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,59%</t>
+          <t>64,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10045,7 +10045,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8119</t>
+          <t>8368</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -10060,7 +10060,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>67,02%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>22681</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>29220</t>
+          <t>29079</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>71,6%</t>
+          <t>72,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>92,78%</t>
         </is>
       </c>
     </row>
@@ -10465,7 +10465,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2897</t>
+          <t>3690</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10480,7 +10480,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -10535,7 +10535,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>3254</t>
+          <t>3326</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10550,7 +10550,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -10576,7 +10576,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2674</t>
+          <t>3228</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10591,7 +10591,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10646,7 +10646,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2525</t>
+          <t>3065</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10661,7 +10661,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -10722,7 +10722,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3301</t>
+          <t>3282</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10737,7 +10737,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10757,7 +10757,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3602</t>
+          <t>4319</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10772,7 +10772,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -10798,7 +10798,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5018</t>
+          <t>5160</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10813,7 +10813,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -10833,7 +10833,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3871</t>
+          <t>4263</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10848,7 +10848,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -10863,12 +10863,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>612</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6578</t>
+          <t>6272</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10878,12 +10878,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,32%</t>
         </is>
       </c>
     </row>
@@ -10904,12 +10904,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5609</t>
+          <t>5501</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14667</t>
+          <t>14769</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10919,12 +10919,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10939,12 +10939,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3886</t>
+          <t>3925</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12171</t>
+          <t>12487</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10954,12 +10954,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10974,12 +10974,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>11214</t>
+          <t>11193</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>23803</t>
+          <t>24638</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10989,12 +10989,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>13,05%</t>
         </is>
       </c>
     </row>
@@ -11015,12 +11015,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>74549</t>
+          <t>74744</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>85007</t>
+          <t>85154</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11030,12 +11030,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>80,31%</t>
+          <t>80,52%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11050,12 +11050,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>82333</t>
+          <t>81565</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>91332</t>
+          <t>90816</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11065,12 +11065,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11085,12 +11085,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>160202</t>
+          <t>159298</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>174332</t>
+          <t>174157</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11100,12 +11100,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,22%</t>
         </is>
       </c>
     </row>
@@ -11909,12 +11909,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>759</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>6473</t>
+          <t>6409</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -11924,12 +11924,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -11944,12 +11944,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1995</t>
+          <t>1918</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>8529</t>
+          <t>8041</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -11959,12 +11959,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -11979,12 +11979,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3856</t>
+          <t>3776</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>11884</t>
+          <t>12003</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -11994,12 +11994,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,54%</t>
         </is>
       </c>
     </row>
@@ -12020,12 +12020,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>24634</t>
+          <t>24698</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>30420</t>
+          <t>30348</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12035,12 +12035,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>79,19%</t>
+          <t>79,4%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12055,12 +12055,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>28806</t>
+          <t>29294</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>35340</t>
+          <t>35417</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12070,12 +12070,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>77,16%</t>
+          <t>78,46%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12090,12 +12090,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>56558</t>
+          <t>56439</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>64586</t>
+          <t>64666</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12105,12 +12105,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>82,64%</t>
+          <t>82,46%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,48%</t>
         </is>
       </c>
     </row>
@@ -12364,7 +12364,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2939</t>
+          <t>2927</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12379,7 +12379,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12434,7 +12434,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>2949</t>
+          <t>3274</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12449,7 +12449,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -12475,7 +12475,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>3313</t>
+          <t>3724</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12490,7 +12490,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12545,7 +12545,7 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>3572</t>
+          <t>3727</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12560,7 +12560,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -12586,7 +12586,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2229</t>
+          <t>2659</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12601,7 +12601,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12656,7 +12656,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>2897</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12697,7 +12697,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>2595</t>
+          <t>3836</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -12712,7 +12712,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -12732,7 +12732,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>3272</t>
+          <t>3309</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -12747,7 +12747,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -12767,7 +12767,7 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>3870</t>
+          <t>4430</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -12782,7 +12782,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -12808,7 +12808,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>4588</t>
+          <t>4787</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -12823,7 +12823,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -12843,7 +12843,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>4128</t>
+          <t>3863</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -12858,7 +12858,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -12873,12 +12873,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>615</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>6377</t>
+          <t>5860</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -12893,7 +12893,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -12914,12 +12914,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>9923</t>
+          <t>9469</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>21205</t>
+          <t>21466</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -12929,12 +12929,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -12949,12 +12949,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>8246</t>
+          <t>8537</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>19064</t>
+          <t>19689</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -12964,12 +12964,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -12984,12 +12984,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>19965</t>
+          <t>20790</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>36049</t>
+          <t>36854</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -12999,12 +12999,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,77%</t>
         </is>
       </c>
     </row>
@@ -13025,12 +13025,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>117981</t>
+          <t>117083</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>130442</t>
+          <t>130659</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -13040,12 +13040,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>82,41%</t>
+          <t>81,78%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -13060,12 +13060,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>124903</t>
+          <t>124365</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>136089</t>
+          <t>135656</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -13075,12 +13075,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -13095,12 +13095,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>246136</t>
+          <t>246342</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>263924</t>
+          <t>263065</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -13110,12 +13110,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>85,35%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,14%</t>
         </is>
       </c>
     </row>
@@ -14079,7 +14079,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2772</t>
+          <t>2585</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -14094,7 +14094,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -14114,7 +14114,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2684</t>
+          <t>2279</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -14129,7 +14129,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>14,26%</t>
         </is>
       </c>
     </row>
@@ -14155,7 +14155,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3133</t>
+          <t>3142</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -14170,7 +14170,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>47,86%</t>
+          <t>48,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -14225,7 +14225,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3367</t>
+          <t>3585</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -14240,7 +14240,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>22,44%</t>
         </is>
       </c>
     </row>
@@ -14261,7 +14261,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3412</t>
+          <t>3403</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -14276,7 +14276,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>52,14%</t>
+          <t>52,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -14296,7 +14296,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6662</t>
+          <t>6849</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -14311,7 +14311,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,62%</t>
+          <t>72,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -14331,7 +14331,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>11741</t>
+          <t>11818</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>73,48%</t>
+          <t>73,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -14827,7 +14827,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4668</t>
+          <t>4190</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -14842,7 +14842,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -14897,7 +14897,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4427</t>
+          <t>3269</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -14912,7 +14912,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -14938,7 +14938,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4126</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -14953,7 +14953,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -14973,7 +14973,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5233</t>
+          <t>4639</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -14988,7 +14988,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -15008,7 +15008,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6157</t>
+          <t>5601</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -15023,7 +15023,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -15084,7 +15084,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3354</t>
+          <t>3667</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -15099,7 +15099,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -15119,7 +15119,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>3120</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -15155,12 +15155,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1483</t>
+          <t>1606</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8017</t>
+          <t>7989</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -15170,12 +15170,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -15190,12 +15190,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2097</t>
+          <t>2407</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11332</t>
+          <t>11221</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -15205,12 +15205,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -15225,12 +15225,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5267</t>
+          <t>5373</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>16756</t>
+          <t>15553</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -15240,12 +15240,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>9,88%</t>
         </is>
       </c>
     </row>
@@ -15266,12 +15266,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>56543</t>
+          <t>56564</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>63982</t>
+          <t>63815</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -15281,12 +15281,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>85,39%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -15301,12 +15301,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>78138</t>
+          <t>77549</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>87529</t>
+          <t>87322</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -15316,12 +15316,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,63%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -15336,12 +15336,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>137110</t>
+          <t>138415</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>149471</t>
+          <t>149570</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -15351,12 +15351,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,97%</t>
         </is>
       </c>
     </row>
@@ -15534,7 +15534,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4469</t>
+          <t>5197</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -15549,7 +15549,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -15569,7 +15569,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5170</t>
+          <t>5678</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -15584,7 +15584,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>9,72%</t>
         </is>
       </c>
     </row>
@@ -15756,7 +15756,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6248</t>
+          <t>4947</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -15771,7 +15771,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -15791,7 +15791,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6135</t>
+          <t>6923</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -15806,7 +15806,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>11,85%</t>
         </is>
       </c>
     </row>
@@ -15867,7 +15867,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2716</t>
+          <t>3321</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -15882,7 +15882,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -15902,7 +15902,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3449</t>
+          <t>2431</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -15917,7 +15917,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -16089,7 +16089,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2625</t>
+          <t>2942</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -16104,7 +16104,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -16124,7 +16124,7 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2723</t>
+          <t>2711</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -16139,7 +16139,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,64%</t>
         </is>
       </c>
     </row>
@@ -16165,7 +16165,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3303</t>
+          <t>3494</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -16180,7 +16180,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -16200,7 +16200,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>4859</t>
+          <t>5257</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -16215,7 +16215,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -16230,12 +16230,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>827</t>
+          <t>597</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6337</t>
+          <t>5824</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -16245,12 +16245,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>9,96%</t>
         </is>
       </c>
     </row>
@@ -16271,7 +16271,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>24228</t>
+          <t>24037</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -16286,7 +16286,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>87,31%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -16306,12 +16306,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>21277</t>
+          <t>21390</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>28893</t>
+          <t>28834</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -16321,12 +16321,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>68,84%</t>
+          <t>69,2%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>47468</t>
+          <t>47390</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>55838</t>
+          <t>55953</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -16356,12 +16356,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>81,09%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,74%</t>
         </is>
       </c>
     </row>
@@ -16539,7 +16539,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>5283</t>
+          <t>5067</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -16554,7 +16554,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -16574,7 +16574,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>5906</t>
+          <t>5981</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -16589,7 +16589,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -16761,7 +16761,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>6162</t>
+          <t>6123</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -16776,7 +16776,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -16796,7 +16796,7 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>6028</t>
+          <t>7228</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -16811,7 +16811,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -16837,7 +16837,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>3515</t>
+          <t>4549</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -16852,7 +16852,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -16872,7 +16872,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3124</t>
+          <t>2976</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -16887,7 +16887,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>4185</t>
+          <t>4374</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -16922,7 +16922,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -16948,7 +16948,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>4409</t>
+          <t>3708</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -16963,7 +16963,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -16983,7 +16983,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>5154</t>
+          <t>6031</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -16998,7 +16998,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -17018,7 +17018,7 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>6152</t>
+          <t>6374</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -17033,7 +17033,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -17089,12 +17089,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>525</t>
+          <t>513</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>4971</t>
+          <t>4825</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -17104,12 +17104,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17124,12 +17124,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>528</t>
+          <t>533</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>4969</t>
+          <t>5077</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -17144,7 +17144,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -17165,12 +17165,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2821</t>
+          <t>2497</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>10226</t>
+          <t>9854</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -17180,12 +17180,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -17200,12 +17200,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>3357</t>
+          <t>3301</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>13171</t>
+          <t>12974</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -17215,12 +17215,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -17235,12 +17235,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>7570</t>
+          <t>7476</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>19365</t>
+          <t>19161</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -17250,12 +17250,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,26%</t>
         </is>
       </c>
     </row>
@@ -17276,12 +17276,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>88025</t>
+          <t>87858</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>96329</t>
+          <t>96606</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -17291,12 +17291,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>87,58%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>111001</t>
+          <t>111627</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>123962</t>
+          <t>123834</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -17326,12 +17326,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>84,83%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -17346,12 +17346,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>202958</t>
+          <t>203340</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>218419</t>
+          <t>217940</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -17361,12 +17361,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>93,98%</t>
         </is>
       </c>
     </row>
